--- a/data/valuations/GOOG/GOOG_modelo_valoracion.xlsx
+++ b/data/valuations/GOOG/GOOG_modelo_valoracion.xlsx
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.134578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.134578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.134578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.134578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.134578243698718</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.129578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.129578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.129578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.129578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.129578243698718</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.139578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.139578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.139578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.139578243698718</v>
+        <v>0.01</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.139578243698718</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="23">
@@ -1076,19 +1076,19 @@
         </is>
       </c>
       <c r="G31" s="6" t="n">
-        <v>0.1483341721272307</v>
+        <v>0.1307056039188442</v>
       </c>
       <c r="H31" s="6" t="n">
-        <v>0.1483341721272307</v>
+        <v>0.1307056039188442</v>
       </c>
       <c r="I31" s="6" t="n">
-        <v>0.1483341721272307</v>
+        <v>0.1307056039188442</v>
       </c>
       <c r="J31" s="6" t="n">
-        <v>0.1483341721272307</v>
+        <v>0.1307056039188442</v>
       </c>
       <c r="K31" s="6" t="n">
-        <v>0.1483341721272307</v>
+        <v>0.1307056039188442</v>
       </c>
     </row>
     <row r="32">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1049</v>
+        <v>0.1051</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0949</v>
+        <v>0.0951</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1149</v>
+        <v>0.1151</v>
       </c>
     </row>
     <row r="38">
@@ -1178,7 +1178,7 @@
         </is>
       </c>
       <c r="C40" s="9" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="41">
@@ -1188,7 +1188,7 @@
         </is>
       </c>
       <c r="C41" s="9" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
     </row>
     <row r="42">
@@ -1198,7 +1198,7 @@
         </is>
       </c>
       <c r="C42" s="9" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>298.79</v>
+        <v>273.76</v>
       </c>
     </row>
     <row r="4">
@@ -3584,7 +3584,7 @@
         </is>
       </c>
       <c r="K21" s="8">
-        <f>K12*$C$16</f>
+        <f>K8*$C$16</f>
         <v/>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/298.79-1</f>
+        <f>C33/273.76-1</f>
         <v/>
       </c>
     </row>
@@ -3727,202 +3727,202 @@
       </c>
       <c r="C38" s="1" t="inlineStr">
         <is>
-          <t>11x</t>
+          <t>14x</t>
         </is>
       </c>
       <c r="D38" s="1" t="inlineStr">
         <is>
-          <t>13x</t>
+          <t>16x</t>
         </is>
       </c>
       <c r="E38" s="1" t="inlineStr">
         <is>
-          <t>15x</t>
+          <t>18x</t>
         </is>
       </c>
       <c r="F38" s="1" t="inlineStr">
         <is>
-          <t>17x</t>
+          <t>20x</t>
         </is>
       </c>
       <c r="G38" s="1" t="inlineStr">
         <is>
-          <t>19x</t>
+          <t>22x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.07489999999999999</v>
+        <v>0.0751</v>
       </c>
       <c r="C39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*11/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*13/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*16/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*15/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*18/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*17/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*20/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G39" s="22">
-        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$12*19/(1+$A$39)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*22/(1+$A$39)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.08489999999999999</v>
+        <v>0.0851</v>
       </c>
       <c r="C40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*11/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*13/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*16/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*15/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*18/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*17/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*20/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G40" s="22">
-        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$12*19/(1+$A$40)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*22/(1+$A$40)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0949</v>
+        <v>0.0951</v>
       </c>
       <c r="C41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*11/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*13/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*16/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*15/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*18/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*17/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*20/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G41" s="22">
-        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$12*19/(1+$A$41)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*22/(1+$A$41)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1049</v>
+        <v>0.1051</v>
       </c>
       <c r="C42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*11/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*13/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*16/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E42" s="23">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*15/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*18/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*17/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*20/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G42" s="22">
-        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$12*19/(1+$A$42)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*22/(1+$A$42)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1149</v>
+        <v>0.1151</v>
       </c>
       <c r="C43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*11/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*13/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*16/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*15/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*18/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*17/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*20/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G43" s="22">
-        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$12*19/(1+$A$43)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*22/(1+$A$43)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1249</v>
+        <v>0.1251</v>
       </c>
       <c r="C44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*11/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*13/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*16/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*15/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*18/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*17/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*20/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G44" s="22">
-        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$12*19/(1+$A$44)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*22/(1+$A$44)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1349</v>
+        <v>0.1351</v>
       </c>
       <c r="C45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*11/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="D45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*13/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*16/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="E45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*15/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*18/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="F45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*17/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*20/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
       <c r="G45" s="22">
-        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$12*19/(1+$A$45)^5+$C$29)/$C$32</f>
+        <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*22/(1+$A$45)^5+$C$29)/$C$32</f>
         <v/>
       </c>
     </row>

--- a/data/valuations/GOOG/GOOG_modelo_valoracion.xlsx
+++ b/data/valuations/GOOG/GOOG_modelo_valoracion.xlsx
@@ -868,19 +868,19 @@
         </is>
       </c>
       <c r="G20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.134578243698718</v>
       </c>
       <c r="H20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.134578243698718</v>
       </c>
       <c r="I20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.134578243698718</v>
       </c>
       <c r="J20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.134578243698718</v>
       </c>
       <c r="K20" s="6" t="n">
-        <v>0.01</v>
+        <v>0.134578243698718</v>
       </c>
     </row>
     <row r="21">
@@ -890,19 +890,19 @@
         </is>
       </c>
       <c r="G21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.129578243698718</v>
       </c>
       <c r="H21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.129578243698718</v>
       </c>
       <c r="I21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.129578243698718</v>
       </c>
       <c r="J21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.129578243698718</v>
       </c>
       <c r="K21" s="6" t="n">
-        <v>0.01</v>
+        <v>0.129578243698718</v>
       </c>
     </row>
     <row r="22">
@@ -912,19 +912,19 @@
         </is>
       </c>
       <c r="G22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.139578243698718</v>
       </c>
       <c r="H22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.139578243698718</v>
       </c>
       <c r="I22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.139578243698718</v>
       </c>
       <c r="J22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.139578243698718</v>
       </c>
       <c r="K22" s="6" t="n">
-        <v>0.01</v>
+        <v>0.139578243698718</v>
       </c>
     </row>
     <row r="23">
@@ -1137,7 +1137,7 @@
         </is>
       </c>
       <c r="C35" s="6" t="n">
-        <v>0.1051</v>
+        <v>0.1059</v>
       </c>
     </row>
     <row r="36">
@@ -1147,7 +1147,7 @@
         </is>
       </c>
       <c r="C36" s="6" t="n">
-        <v>0.0951</v>
+        <v>0.0959</v>
       </c>
     </row>
     <row r="37">
@@ -1157,7 +1157,7 @@
         </is>
       </c>
       <c r="C37" s="6" t="n">
-        <v>0.1151</v>
+        <v>0.1159</v>
       </c>
     </row>
     <row r="38">
@@ -3285,7 +3285,7 @@
         </is>
       </c>
       <c r="F2" s="16" t="n">
-        <v>273.76</v>
+        <v>294.46</v>
       </c>
     </row>
     <row r="4">
@@ -3698,7 +3698,7 @@
         </is>
       </c>
       <c r="C34" s="20">
-        <f>C33/273.76-1</f>
+        <f>C33/294.46-1</f>
         <v/>
       </c>
     </row>
@@ -3753,7 +3753,7 @@
     </row>
     <row r="39">
       <c r="A39" s="21" t="n">
-        <v>0.0751</v>
+        <v>0.0759</v>
       </c>
       <c r="C39" s="22">
         <f>(G$12/(1+$A$39)^1+H$12/(1+$A$39)^2+I$12/(1+$A$39)^3+J$12/(1+$A$39)^4+K$12/(1+$A$39)^5+K$8*14/(1+$A$39)^5+$C$29)/$C$32</f>
@@ -3778,7 +3778,7 @@
     </row>
     <row r="40">
       <c r="A40" s="21" t="n">
-        <v>0.0851</v>
+        <v>0.08589999999999999</v>
       </c>
       <c r="C40" s="22">
         <f>(G$12/(1+$A$40)^1+H$12/(1+$A$40)^2+I$12/(1+$A$40)^3+J$12/(1+$A$40)^4+K$12/(1+$A$40)^5+K$8*14/(1+$A$40)^5+$C$29)/$C$32</f>
@@ -3803,7 +3803,7 @@
     </row>
     <row r="41">
       <c r="A41" s="21" t="n">
-        <v>0.0951</v>
+        <v>0.0959</v>
       </c>
       <c r="C41" s="22">
         <f>(G$12/(1+$A$41)^1+H$12/(1+$A$41)^2+I$12/(1+$A$41)^3+J$12/(1+$A$41)^4+K$12/(1+$A$41)^5+K$8*14/(1+$A$41)^5+$C$29)/$C$32</f>
@@ -3828,7 +3828,7 @@
     </row>
     <row r="42">
       <c r="A42" s="21" t="n">
-        <v>0.1051</v>
+        <v>0.1059</v>
       </c>
       <c r="C42" s="22">
         <f>(G$12/(1+$A$42)^1+H$12/(1+$A$42)^2+I$12/(1+$A$42)^3+J$12/(1+$A$42)^4+K$12/(1+$A$42)^5+K$8*14/(1+$A$42)^5+$C$29)/$C$32</f>
@@ -3853,7 +3853,7 @@
     </row>
     <row r="43">
       <c r="A43" s="21" t="n">
-        <v>0.1151</v>
+        <v>0.1159</v>
       </c>
       <c r="C43" s="22">
         <f>(G$12/(1+$A$43)^1+H$12/(1+$A$43)^2+I$12/(1+$A$43)^3+J$12/(1+$A$43)^4+K$12/(1+$A$43)^5+K$8*14/(1+$A$43)^5+$C$29)/$C$32</f>
@@ -3878,7 +3878,7 @@
     </row>
     <row r="44">
       <c r="A44" s="21" t="n">
-        <v>0.1251</v>
+        <v>0.1259</v>
       </c>
       <c r="C44" s="22">
         <f>(G$12/(1+$A$44)^1+H$12/(1+$A$44)^2+I$12/(1+$A$44)^3+J$12/(1+$A$44)^4+K$12/(1+$A$44)^5+K$8*14/(1+$A$44)^5+$C$29)/$C$32</f>
@@ -3903,7 +3903,7 @@
     </row>
     <row r="45">
       <c r="A45" s="21" t="n">
-        <v>0.1351</v>
+        <v>0.1359</v>
       </c>
       <c r="C45" s="22">
         <f>(G$12/(1+$A$45)^1+H$12/(1+$A$45)^2+I$12/(1+$A$45)^3+J$12/(1+$A$45)^4+K$12/(1+$A$45)^5+K$8*14/(1+$A$45)^5+$C$29)/$C$32</f>
